--- a/src/test/hough-image-create/du_drone_gray-151x118-sobel-0.hough.xlsx
+++ b/src/test/hough-image-create/du_drone_gray-151x118-sobel-0.hough.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kushn\Dropbox\software\projects\cv\local\cv-workbench\src\test\hough-image-create\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:40009_{A6AD6D31-C533-499D-B8D6-C7B876F9C83A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:40009_{51326613-A05B-4372-B648-F6DC17FCCB29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420"/>
   </bookViews>
@@ -338,7 +338,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -453,35 +453,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -527,11 +498,8 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -577,11 +545,11 @@
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
     <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="2">
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFF0000"/>
+          <bgColor rgb="FFFF6D6D"/>
         </patternFill>
       </fill>
     </dxf>
@@ -592,15 +560,13 @@
         </patternFill>
       </fill>
     </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFFF6D6D"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -912,221 +878,603 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:W8"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="8.7265625" style="1"/>
+    <col min="1" max="1" width="5.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.453125" customWidth="1"/>
+    <col min="3" max="4" width="5.453125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.81640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="12" width="5.453125" bestFit="1" customWidth="1"/>
+    <col min="13" max="22" width="4.81640625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="4.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="2">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A1">
         <v>-95.5</v>
       </c>
-      <c r="B1" s="3">
+      <c r="C1">
+        <v>-65.5</v>
+      </c>
+      <c r="D1">
+        <v>-64.5</v>
+      </c>
+      <c r="E1">
         <v>-63.5</v>
       </c>
-      <c r="C1" s="3">
+      <c r="F1">
         <v>-62.5</v>
       </c>
-      <c r="D1" s="3">
+      <c r="G1">
         <v>-61.5</v>
       </c>
-      <c r="E1" s="3">
+      <c r="H1">
         <v>-60.5</v>
       </c>
-      <c r="F1" s="3">
+      <c r="I1">
         <v>-59.5</v>
       </c>
-      <c r="G1" s="3">
+      <c r="J1">
         <v>-58.5</v>
       </c>
-      <c r="H1" s="3">
+      <c r="K1">
         <v>-57.5</v>
       </c>
-      <c r="I1" s="3">
+      <c r="L1">
+        <v>-56.5</v>
+      </c>
+      <c r="M1">
+        <v>58.5</v>
+      </c>
+      <c r="N1">
         <v>59.5</v>
       </c>
-      <c r="J1" s="3">
+      <c r="O1">
+        <v>60.5</v>
+      </c>
+      <c r="P1">
+        <v>61.5</v>
+      </c>
+      <c r="Q1">
+        <v>62.5</v>
+      </c>
+      <c r="R1">
+        <v>63.5</v>
+      </c>
+      <c r="S1">
+        <v>64.5</v>
+      </c>
+      <c r="T1">
         <v>65.5</v>
       </c>
+      <c r="U1">
+        <v>66.5</v>
+      </c>
+      <c r="V1">
+        <v>67.5</v>
+      </c>
+      <c r="W1">
+        <v>68.5</v>
+      </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A2" s="1">
+    <row r="2" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A2">
         <v>0</v>
       </c>
       <c r="B2">
+        <f>A2/3</f>
+        <v>0</v>
+      </c>
+      <c r="C2">
+        <v>259</v>
+      </c>
+      <c r="D2">
+        <v>3353</v>
+      </c>
+      <c r="E2">
         <v>11858</v>
       </c>
-      <c r="C2">
+      <c r="F2">
         <v>9728</v>
       </c>
-      <c r="D2">
+      <c r="G2">
         <v>192</v>
       </c>
-      <c r="E2">
+      <c r="H2">
         <v>0</v>
       </c>
-      <c r="F2">
+      <c r="I2">
         <v>2954</v>
       </c>
-      <c r="G2">
+      <c r="J2">
         <v>9128</v>
       </c>
-      <c r="H2">
+      <c r="K2">
         <v>7555</v>
       </c>
-      <c r="I2">
+      <c r="L2">
+        <v>2530</v>
+      </c>
+      <c r="M2">
+        <v>1724</v>
+      </c>
+      <c r="N2">
         <v>1842</v>
       </c>
-      <c r="J2">
+      <c r="O2">
+        <v>1525</v>
+      </c>
+      <c r="P2">
+        <v>765</v>
+      </c>
+      <c r="Q2">
+        <v>1336</v>
+      </c>
+      <c r="R2">
+        <v>1410</v>
+      </c>
+      <c r="S2">
+        <v>490</v>
+      </c>
+      <c r="T2">
         <v>7896</v>
       </c>
+      <c r="U2">
+        <v>4884</v>
+      </c>
+      <c r="V2">
+        <v>3500</v>
+      </c>
+      <c r="W2">
+        <v>1299</v>
+      </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A3" s="1">
+    <row r="3" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A3">
         <v>3</v>
       </c>
       <c r="B3">
+        <f t="shared" ref="B3:B8" si="0">A3/3</f>
+        <v>1</v>
+      </c>
+      <c r="C3">
+        <v>2326</v>
+      </c>
+      <c r="D3">
+        <v>5634</v>
+      </c>
+      <c r="E3">
         <v>5283</v>
       </c>
-      <c r="C3">
+      <c r="F3">
         <v>6690</v>
       </c>
-      <c r="D3">
+      <c r="G3">
         <v>4994</v>
       </c>
-      <c r="E3">
+      <c r="H3">
         <v>3502</v>
       </c>
-      <c r="F3">
+      <c r="I3">
         <v>5549</v>
       </c>
-      <c r="G3">
+      <c r="J3">
         <v>5312</v>
       </c>
-      <c r="H3">
+      <c r="K3">
         <v>4557</v>
       </c>
-      <c r="I3">
+      <c r="L3">
+        <v>2194</v>
+      </c>
+      <c r="M3">
+        <v>1537</v>
+      </c>
+      <c r="N3">
         <v>1048</v>
       </c>
-      <c r="J3">
+      <c r="O3">
+        <v>1044</v>
+      </c>
+      <c r="P3">
+        <v>63</v>
+      </c>
+      <c r="Q3">
+        <v>61</v>
+      </c>
+      <c r="R3">
+        <v>2953</v>
+      </c>
+      <c r="S3">
+        <v>4962</v>
+      </c>
+      <c r="T3">
         <v>4518</v>
       </c>
+      <c r="U3">
+        <v>4295</v>
+      </c>
+      <c r="V3">
+        <v>3205</v>
+      </c>
+      <c r="W3">
+        <v>951</v>
+      </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A4" s="1">
+    <row r="4" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A4">
         <v>6</v>
       </c>
       <c r="B4">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="C4">
+        <v>2916</v>
+      </c>
+      <c r="D4">
+        <v>2465</v>
+      </c>
+      <c r="E4">
         <v>3960</v>
       </c>
-      <c r="C4">
+      <c r="F4">
         <v>3760</v>
       </c>
-      <c r="D4">
+      <c r="G4">
         <v>4786</v>
       </c>
-      <c r="E4">
+      <c r="H4">
         <v>6752</v>
       </c>
-      <c r="F4">
+      <c r="I4">
         <v>6489</v>
       </c>
-      <c r="G4">
+      <c r="J4">
         <v>3719</v>
       </c>
-      <c r="H4">
+      <c r="K4">
         <v>3399</v>
       </c>
-      <c r="I4">
+      <c r="L4">
+        <v>3077</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4">
         <v>415</v>
       </c>
-      <c r="J4">
+      <c r="O4">
+        <v>596</v>
+      </c>
+      <c r="P4">
+        <v>1790</v>
+      </c>
+      <c r="Q4">
+        <v>2421</v>
+      </c>
+      <c r="R4">
+        <v>2037</v>
+      </c>
+      <c r="S4">
+        <v>2967</v>
+      </c>
+      <c r="T4">
         <v>4428</v>
       </c>
+      <c r="U4">
+        <v>2997</v>
+      </c>
+      <c r="V4">
+        <v>2872</v>
+      </c>
+      <c r="W4">
+        <v>2527</v>
+      </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A5" s="1">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A5">
         <v>9</v>
       </c>
       <c r="B5">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="C5">
+        <v>2092</v>
+      </c>
+      <c r="D5">
+        <v>2478</v>
+      </c>
+      <c r="E5">
         <v>2649</v>
       </c>
-      <c r="C5">
+      <c r="F5">
         <v>4463</v>
       </c>
-      <c r="D5">
+      <c r="G5">
         <v>3840</v>
       </c>
-      <c r="E5">
+      <c r="H5">
         <v>3135</v>
       </c>
-      <c r="F5">
+      <c r="I5">
         <v>4147</v>
       </c>
-      <c r="G5">
+      <c r="J5">
         <v>4662</v>
       </c>
-      <c r="H5">
+      <c r="K5">
         <v>4956</v>
       </c>
-      <c r="I5">
+      <c r="L5">
+        <v>3881</v>
+      </c>
+      <c r="M5">
+        <v>329</v>
+      </c>
+      <c r="N5">
         <v>1384</v>
       </c>
-      <c r="J5">
+      <c r="O5">
+        <v>1489</v>
+      </c>
+      <c r="P5">
+        <v>1661</v>
+      </c>
+      <c r="Q5">
+        <v>2737</v>
+      </c>
+      <c r="R5">
+        <v>2648</v>
+      </c>
+      <c r="S5">
+        <v>1977</v>
+      </c>
+      <c r="T5">
         <v>2216</v>
       </c>
+      <c r="U5">
+        <v>3477</v>
+      </c>
+      <c r="V5">
+        <v>2160</v>
+      </c>
+      <c r="W5">
+        <v>2367</v>
+      </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A6" s="1">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>171</v>
+      </c>
+      <c r="B6">
+        <f t="shared" si="0"/>
+        <v>57</v>
+      </c>
+      <c r="C6">
+        <v>2748</v>
+      </c>
+      <c r="D6">
+        <v>3032</v>
+      </c>
+      <c r="E6">
+        <v>2817</v>
+      </c>
+      <c r="F6">
+        <v>2909</v>
+      </c>
+      <c r="G6">
+        <v>2692</v>
+      </c>
+      <c r="H6">
+        <v>1601</v>
+      </c>
+      <c r="I6">
+        <v>1232</v>
+      </c>
+      <c r="J6">
+        <v>1360</v>
+      </c>
+      <c r="K6">
+        <v>735</v>
+      </c>
+      <c r="L6">
+        <v>657</v>
+      </c>
+      <c r="M6">
+        <v>3345</v>
+      </c>
+      <c r="N6">
+        <v>3359</v>
+      </c>
+      <c r="O6">
+        <v>3805</v>
+      </c>
+      <c r="P6">
+        <v>4417</v>
+      </c>
+      <c r="Q6">
+        <v>3821</v>
+      </c>
+      <c r="R6">
+        <v>3348</v>
+      </c>
+      <c r="S6">
+        <v>3989</v>
+      </c>
+      <c r="T6">
+        <v>2705</v>
+      </c>
+      <c r="U6">
+        <v>1823</v>
+      </c>
+      <c r="V6">
+        <v>2716</v>
+      </c>
+      <c r="W6">
+        <v>2491</v>
+      </c>
+    </row>
+    <row r="7" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>174</v>
+      </c>
+      <c r="B7">
+        <f t="shared" si="0"/>
+        <v>58</v>
+      </c>
+      <c r="C7">
+        <v>3547</v>
+      </c>
+      <c r="D7">
+        <v>3081</v>
+      </c>
+      <c r="E7">
+        <v>3302</v>
+      </c>
+      <c r="F7">
+        <v>2913</v>
+      </c>
+      <c r="G7">
+        <v>3559</v>
+      </c>
+      <c r="H7">
+        <v>2635</v>
+      </c>
+      <c r="I7">
+        <v>1890</v>
+      </c>
+      <c r="J7">
+        <v>147</v>
+      </c>
+      <c r="K7">
+        <v>727</v>
+      </c>
+      <c r="L7">
+        <v>915</v>
+      </c>
+      <c r="M7">
+        <v>3715</v>
+      </c>
+      <c r="N7">
+        <v>3392</v>
+      </c>
+      <c r="O7">
+        <v>2739</v>
+      </c>
+      <c r="P7">
+        <v>4938</v>
+      </c>
+      <c r="Q7">
+        <v>5766</v>
+      </c>
+      <c r="R7">
+        <v>3321</v>
+      </c>
+      <c r="S7">
+        <v>3000</v>
+      </c>
+      <c r="T7">
+        <v>2440</v>
+      </c>
+      <c r="U7">
+        <v>3025</v>
+      </c>
+      <c r="V7">
+        <v>5451</v>
+      </c>
+      <c r="W7">
+        <v>3778</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A8">
         <v>177</v>
       </c>
-      <c r="B6">
+      <c r="B8">
+        <f t="shared" si="0"/>
+        <v>59</v>
+      </c>
+      <c r="C8">
+        <v>2413</v>
+      </c>
+      <c r="D8">
+        <v>4473</v>
+      </c>
+      <c r="E8">
         <v>4755</v>
       </c>
-      <c r="C6">
+      <c r="F8">
         <v>4170</v>
       </c>
-      <c r="D6">
+      <c r="G8">
         <v>2286</v>
       </c>
-      <c r="E6">
+      <c r="H8">
         <v>1488</v>
       </c>
-      <c r="F6">
+      <c r="I8">
         <v>2209</v>
       </c>
-      <c r="G6">
+      <c r="J8">
         <v>2108</v>
       </c>
-      <c r="H6">
+      <c r="K8">
         <v>511</v>
       </c>
-      <c r="I6">
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8">
+        <v>4057</v>
+      </c>
+      <c r="N8">
         <v>6126</v>
       </c>
-      <c r="J6">
+      <c r="O8">
+        <v>5615</v>
+      </c>
+      <c r="P8">
+        <v>3893</v>
+      </c>
+      <c r="Q8">
+        <v>1755</v>
+      </c>
+      <c r="R8">
+        <v>3547</v>
+      </c>
+      <c r="S8">
+        <v>5987</v>
+      </c>
+      <c r="T8">
         <v>4651</v>
+      </c>
+      <c r="U8">
+        <v>5466</v>
+      </c>
+      <c r="V8">
+        <v>3685</v>
+      </c>
+      <c r="W8">
+        <v>1080</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="cellIs" dxfId="2" priority="1" operator="between">
-      <formula>6000</formula>
-      <formula>8000</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="between">
-      <formula>8000</formula>
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="between">
+      <formula>5000</formula>
       <formula>10000</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="3" operator="between">
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="between">
       <formula>10000</formula>
-      <formula>12000</formula>
+      <formula>15000</formula>
     </cfRule>
   </conditionalFormatting>
   <printOptions gridLines="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>